--- a/policy_20260801.xlsx
+++ b/policy_20260801.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ETW\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FEB737-328D-408A-A154-5706A2672C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AED7530-D5B7-4565-B063-557BA978A5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="3435" windowWidth="26505" windowHeight="14550" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5160" yWindow="3360" windowWidth="26505" windowHeight="14550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="추가지원금" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="U_공통지원금" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">추가지원금!$A$1:$Q$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">추가지원금!$A$1:$Q$25</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="41">
   <si>
     <t>모델명</t>
   </si>
@@ -477,9 +477,6 @@
     <t>S25 엣지 256G</t>
   </si>
   <si>
-    <t>Z 플립8 256G</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -764,6 +761,212 @@
         <charset val="129"/>
       </rPr>
       <t>갤</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>플립</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8 256G</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>폴드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>울트라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 512G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사전예약)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>폴드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와이드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 512G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사전예약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>플립</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8 512G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사전예약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>)</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1063,19 +1266,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:R1001"/>
+  <dimension ref="A1:S1004"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1083,67 +1286,67 @@
         <v>34</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="H1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="J1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="N1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
         <v>350000</v>
       </c>
-      <c r="C2" s="4">
-        <v>0</v>
-      </c>
       <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
         <v>400000</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0</v>
       </c>
       <c r="F2" s="2">
         <v>350000</v>
@@ -1161,10 +1364,10 @@
         <v>350000</v>
       </c>
       <c r="K2" s="2">
+        <v>350000</v>
+      </c>
+      <c r="L2" s="2">
         <v>30000</v>
-      </c>
-      <c r="L2" s="2">
-        <v>350000</v>
       </c>
       <c r="M2" s="2">
         <v>30000</v>
@@ -1173,85 +1376,85 @@
         <v>350000</v>
       </c>
       <c r="O2" s="2">
+        <v>350000</v>
+      </c>
+      <c r="P2" s="2">
         <v>50000</v>
-      </c>
-      <c r="P2" s="2">
-        <v>350000</v>
       </c>
       <c r="Q2" s="2">
         <v>50000</v>
       </c>
-      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
         <v>290000</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
       <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
         <v>340000</v>
       </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
       <c r="F3" s="2">
+        <v>350000</v>
+      </c>
+      <c r="G3" s="2">
         <v>290000</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="2">
+        <v>400000</v>
+      </c>
+      <c r="I3" s="2">
+        <v>340000</v>
+      </c>
+      <c r="J3" s="2">
         <v>350000</v>
       </c>
-      <c r="H3" s="2">
-        <v>340000</v>
-      </c>
-      <c r="I3" s="2">
-        <v>400000</v>
-      </c>
-      <c r="J3" s="2">
+      <c r="K3" s="2">
         <v>290000</v>
       </c>
-      <c r="K3" s="2">
+      <c r="L3" s="2">
         <v>30000</v>
-      </c>
-      <c r="L3" s="2">
-        <v>350000</v>
       </c>
       <c r="M3" s="2">
         <v>30000</v>
       </c>
       <c r="N3" s="2">
+        <v>350000</v>
+      </c>
+      <c r="O3" s="2">
         <v>290000</v>
       </c>
-      <c r="O3" s="2">
+      <c r="P3" s="2">
         <v>50000</v>
-      </c>
-      <c r="P3" s="2">
-        <v>350000</v>
       </c>
       <c r="Q3" s="2">
         <v>50000</v>
       </c>
-      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
         <v>350000</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
       <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
         <v>400000</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0</v>
       </c>
       <c r="F4" s="2">
         <v>350000</v>
@@ -1269,10 +1472,10 @@
         <v>350000</v>
       </c>
       <c r="K4" s="2">
+        <v>350000</v>
+      </c>
+      <c r="L4" s="2">
         <v>30000</v>
-      </c>
-      <c r="L4" s="2">
-        <v>350000</v>
       </c>
       <c r="M4" s="2">
         <v>30000</v>
@@ -1281,17 +1484,17 @@
         <v>350000</v>
       </c>
       <c r="O4" s="2">
+        <v>350000</v>
+      </c>
+      <c r="P4" s="2">
         <v>50000</v>
-      </c>
-      <c r="P4" s="2">
-        <v>350000</v>
       </c>
       <c r="Q4" s="2">
         <v>50000</v>
       </c>
-      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -1323,10 +1526,10 @@
         <v>300000</v>
       </c>
       <c r="K5" s="2">
+        <v>300000</v>
+      </c>
+      <c r="L5" s="2">
         <v>30000</v>
-      </c>
-      <c r="L5" s="2">
-        <v>300000</v>
       </c>
       <c r="M5" s="2">
         <v>30000</v>
@@ -1335,17 +1538,17 @@
         <v>350000</v>
       </c>
       <c r="O5" s="2">
+        <v>350000</v>
+      </c>
+      <c r="P5" s="2">
         <v>50000</v>
-      </c>
-      <c r="P5" s="2">
-        <v>350000</v>
       </c>
       <c r="Q5" s="2">
         <v>50000</v>
       </c>
-      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -1377,10 +1580,10 @@
         <v>300000</v>
       </c>
       <c r="K6" s="2">
+        <v>300000</v>
+      </c>
+      <c r="L6" s="2">
         <v>30000</v>
-      </c>
-      <c r="L6" s="2">
-        <v>300000</v>
       </c>
       <c r="M6" s="2">
         <v>30000</v>
@@ -1389,17 +1592,17 @@
         <v>350000</v>
       </c>
       <c r="O6" s="2">
+        <v>350000</v>
+      </c>
+      <c r="P6" s="2">
         <v>50000</v>
-      </c>
-      <c r="P6" s="2">
-        <v>350000</v>
       </c>
       <c r="Q6" s="2">
         <v>50000</v>
       </c>
-      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -1431,10 +1634,10 @@
         <v>300000</v>
       </c>
       <c r="K7" s="2">
+        <v>300000</v>
+      </c>
+      <c r="L7" s="2">
         <v>30000</v>
-      </c>
-      <c r="L7" s="2">
-        <v>300000</v>
       </c>
       <c r="M7" s="2">
         <v>30000</v>
@@ -1443,17 +1646,17 @@
         <v>350000</v>
       </c>
       <c r="O7" s="2">
+        <v>350000</v>
+      </c>
+      <c r="P7" s="2">
         <v>50000</v>
-      </c>
-      <c r="P7" s="2">
-        <v>350000</v>
       </c>
       <c r="Q7" s="2">
         <v>50000</v>
       </c>
-      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -1485,10 +1688,10 @@
         <v>300000</v>
       </c>
       <c r="K8" s="2">
+        <v>300000</v>
+      </c>
+      <c r="L8" s="2">
         <v>30000</v>
-      </c>
-      <c r="L8" s="2">
-        <v>300000</v>
       </c>
       <c r="M8" s="2">
         <v>30000</v>
@@ -1497,17 +1700,17 @@
         <v>350000</v>
       </c>
       <c r="O8" s="2">
+        <v>350000</v>
+      </c>
+      <c r="P8" s="2">
         <v>50000</v>
-      </c>
-      <c r="P8" s="2">
-        <v>350000</v>
       </c>
       <c r="Q8" s="2">
         <v>50000</v>
       </c>
-      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -1539,10 +1742,10 @@
         <v>300000</v>
       </c>
       <c r="K9" s="2">
+        <v>300000</v>
+      </c>
+      <c r="L9" s="2">
         <v>30000</v>
-      </c>
-      <c r="L9" s="2">
-        <v>300000</v>
       </c>
       <c r="M9" s="2">
         <v>30000</v>
@@ -1551,17 +1754,17 @@
         <v>350000</v>
       </c>
       <c r="O9" s="2">
+        <v>350000</v>
+      </c>
+      <c r="P9" s="2">
         <v>50000</v>
-      </c>
-      <c r="P9" s="2">
-        <v>350000</v>
       </c>
       <c r="Q9" s="2">
         <v>50000</v>
       </c>
-      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -1593,10 +1796,10 @@
         <v>300000</v>
       </c>
       <c r="K10" s="2">
+        <v>300000</v>
+      </c>
+      <c r="L10" s="2">
         <v>30000</v>
-      </c>
-      <c r="L10" s="2">
-        <v>300000</v>
       </c>
       <c r="M10" s="2">
         <v>30000</v>
@@ -1605,17 +1808,17 @@
         <v>350000</v>
       </c>
       <c r="O10" s="2">
+        <v>350000</v>
+      </c>
+      <c r="P10" s="2">
         <v>50000</v>
-      </c>
-      <c r="P10" s="2">
-        <v>350000</v>
       </c>
       <c r="Q10" s="2">
         <v>50000</v>
       </c>
-      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -1644,32 +1847,32 @@
         <v>500000</v>
       </c>
       <c r="J11" s="2">
+        <v>300000</v>
+      </c>
+      <c r="K11" s="2">
         <v>200000</v>
       </c>
-      <c r="K11" s="2">
+      <c r="L11" s="2">
         <v>30000</v>
-      </c>
-      <c r="L11" s="2">
-        <v>300000</v>
       </c>
       <c r="M11" s="2">
         <v>30000</v>
       </c>
       <c r="N11" s="2">
+        <v>350000</v>
+      </c>
+      <c r="O11" s="2">
         <v>250000</v>
       </c>
-      <c r="O11" s="2">
+      <c r="P11" s="2">
         <v>50000</v>
-      </c>
-      <c r="P11" s="2">
-        <v>350000</v>
       </c>
       <c r="Q11" s="2">
         <v>50000</v>
       </c>
-      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
     </row>
-    <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -1698,32 +1901,32 @@
         <v>0</v>
       </c>
       <c r="J12" s="2">
+        <v>300000</v>
+      </c>
+      <c r="K12" s="2">
         <v>200000</v>
       </c>
-      <c r="K12" s="2">
+      <c r="L12" s="2">
         <v>30000</v>
-      </c>
-      <c r="L12" s="2">
-        <v>300000</v>
       </c>
       <c r="M12" s="2">
         <v>30000</v>
       </c>
       <c r="N12" s="2">
+        <v>350000</v>
+      </c>
+      <c r="O12" s="2">
         <v>250000</v>
       </c>
-      <c r="O12" s="2">
+      <c r="P12" s="2">
         <v>50000</v>
-      </c>
-      <c r="P12" s="2">
-        <v>350000</v>
       </c>
       <c r="Q12" s="2">
         <v>50000</v>
       </c>
-      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
     </row>
-    <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -1752,32 +1955,32 @@
         <v>500000</v>
       </c>
       <c r="J13" s="2">
+        <v>300000</v>
+      </c>
+      <c r="K13" s="2">
         <v>200000</v>
       </c>
-      <c r="K13" s="2">
+      <c r="L13" s="2">
         <v>30000</v>
-      </c>
-      <c r="L13" s="2">
-        <v>300000</v>
       </c>
       <c r="M13" s="2">
         <v>30000</v>
       </c>
       <c r="N13" s="2">
+        <v>350000</v>
+      </c>
+      <c r="O13" s="2">
         <v>250000</v>
       </c>
-      <c r="O13" s="2">
+      <c r="P13" s="2">
         <v>50000</v>
-      </c>
-      <c r="P13" s="2">
-        <v>350000</v>
       </c>
       <c r="Q13" s="2">
         <v>50000</v>
       </c>
-      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
     </row>
-    <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -1806,32 +2009,32 @@
         <v>500000</v>
       </c>
       <c r="J14" s="2">
+        <v>300000</v>
+      </c>
+      <c r="K14" s="2">
         <v>200000</v>
       </c>
-      <c r="K14" s="2">
+      <c r="L14" s="2">
         <v>30000</v>
-      </c>
-      <c r="L14" s="2">
-        <v>300000</v>
       </c>
       <c r="M14" s="2">
         <v>30000</v>
       </c>
       <c r="N14" s="2">
+        <v>350000</v>
+      </c>
+      <c r="O14" s="2">
         <v>250000</v>
       </c>
-      <c r="O14" s="2">
+      <c r="P14" s="2">
         <v>50000</v>
-      </c>
-      <c r="P14" s="2">
-        <v>350000</v>
       </c>
       <c r="Q14" s="2">
         <v>50000</v>
       </c>
-      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
     </row>
-    <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -1883,9 +2086,9 @@
       <c r="Q15" s="2">
         <v>0</v>
       </c>
-      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
     </row>
-    <row r="16" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
@@ -1914,416 +2117,518 @@
         <v>445900</v>
       </c>
       <c r="J16" s="2">
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="K16" s="2">
         <v>30000</v>
       </c>
       <c r="L16" s="2">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="M16" s="2">
         <v>30000</v>
       </c>
       <c r="N16" s="2">
+        <v>200000</v>
+      </c>
+      <c r="O16" s="2">
         <v>80000</v>
       </c>
-      <c r="O16" s="2">
+      <c r="P16" s="2">
         <v>50000</v>
-      </c>
-      <c r="P16" s="2">
-        <v>200000</v>
       </c>
       <c r="Q16" s="2">
         <v>50000</v>
       </c>
-      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B17" s="4">
         <v>0</v>
       </c>
       <c r="C17" s="4">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="D17" s="4">
         <v>0</v>
       </c>
       <c r="E17" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="F17" s="2">
-        <v>390000</v>
+        <v>350000</v>
       </c>
       <c r="G17" s="2">
-        <v>390000</v>
+        <v>350000</v>
       </c>
       <c r="H17" s="2">
-        <v>500000</v>
+        <v>400000</v>
       </c>
       <c r="I17" s="2">
-        <v>500000</v>
+        <v>400000</v>
       </c>
       <c r="J17" s="2">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="K17" s="2">
+        <v>350000</v>
+      </c>
+      <c r="L17" s="2">
         <v>30000</v>
-      </c>
-      <c r="L17" s="2">
-        <v>0</v>
       </c>
       <c r="M17" s="2">
         <v>30000</v>
       </c>
       <c r="N17" s="2">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="O17" s="2">
+        <v>350000</v>
+      </c>
+      <c r="P17" s="2">
         <v>50000</v>
-      </c>
-      <c r="P17" s="2">
-        <v>0</v>
       </c>
       <c r="Q17" s="2">
         <v>50000</v>
       </c>
-      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B18" s="4">
         <v>0</v>
       </c>
       <c r="C18" s="4">
-        <v>0</v>
+        <v>290000</v>
       </c>
       <c r="D18" s="4">
         <v>0</v>
       </c>
       <c r="E18" s="4">
-        <v>0</v>
+        <v>340000</v>
       </c>
       <c r="F18" s="2">
-        <v>390000</v>
+        <v>350000</v>
       </c>
       <c r="G18" s="2">
-        <v>390000</v>
+        <v>290000</v>
       </c>
       <c r="H18" s="2">
-        <v>500000</v>
+        <v>400000</v>
       </c>
       <c r="I18" s="2">
-        <v>500000</v>
+        <v>340000</v>
       </c>
       <c r="J18" s="2">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="K18" s="2">
+        <v>290000</v>
+      </c>
+      <c r="L18" s="2">
         <v>30000</v>
-      </c>
-      <c r="L18" s="2">
-        <v>0</v>
       </c>
       <c r="M18" s="2">
         <v>30000</v>
       </c>
       <c r="N18" s="2">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="O18" s="2">
+        <v>290000</v>
+      </c>
+      <c r="P18" s="2">
         <v>50000</v>
-      </c>
-      <c r="P18" s="2">
-        <v>0</v>
       </c>
       <c r="Q18" s="2">
         <v>50000</v>
       </c>
-      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>28</v>
+    <row r="19" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="B19" s="4">
         <v>0</v>
       </c>
       <c r="C19" s="4">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="D19" s="4">
         <v>0</v>
       </c>
       <c r="E19" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="F19" s="2">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="G19" s="2">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="H19" s="2">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="J19" s="2">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="K19" s="2">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="L19" s="2">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="M19" s="2">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="N19" s="2">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="O19" s="2">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="P19" s="2">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="Q19" s="2">
-        <v>0</v>
-      </c>
-      <c r="R19" s="1"/>
+        <v>50000</v>
+      </c>
+      <c r="S19" s="1"/>
     </row>
-    <row r="20" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="4">
+        <v>0</v>
+      </c>
+      <c r="C20" s="4">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>390000</v>
+      </c>
+      <c r="G20" s="2">
+        <v>390000</v>
+      </c>
+      <c r="H20" s="2">
+        <v>500000</v>
+      </c>
+      <c r="I20" s="2">
+        <v>500000</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2">
+        <v>30000</v>
+      </c>
+      <c r="M20" s="2">
+        <v>30000</v>
+      </c>
+      <c r="N20" s="2">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2">
+        <v>50000</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>50000</v>
+      </c>
+      <c r="S20" s="1"/>
+    </row>
+    <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="4">
+        <v>0</v>
+      </c>
+      <c r="C21" s="4">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>390000</v>
+      </c>
+      <c r="G21" s="2">
+        <v>390000</v>
+      </c>
+      <c r="H21" s="2">
+        <v>500000</v>
+      </c>
+      <c r="I21" s="2">
+        <v>500000</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2">
+        <v>30000</v>
+      </c>
+      <c r="M21" s="2">
+        <v>30000</v>
+      </c>
+      <c r="N21" s="2">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2">
+        <v>50000</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>50000</v>
+      </c>
+      <c r="S21" s="1"/>
+    </row>
+    <row r="22" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="4">
+        <v>0</v>
+      </c>
+      <c r="C22" s="4">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="1"/>
+    </row>
+    <row r="23" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="4">
-        <v>0</v>
-      </c>
-      <c r="C20" s="4">
-        <v>0</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" s="4">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0</v>
-      </c>
-      <c r="G20" s="2">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2">
+      <c r="B23" s="4">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2">
+        <v>100000</v>
+      </c>
+      <c r="K23" s="2">
         <v>30000</v>
       </c>
-      <c r="K20" s="2">
+      <c r="L23" s="2">
+        <v>100000</v>
+      </c>
+      <c r="M23" s="2">
         <v>30000</v>
       </c>
-      <c r="L20" s="2">
+      <c r="N23" s="2">
         <v>100000</v>
       </c>
-      <c r="M20" s="2">
+      <c r="O23" s="2">
+        <v>30000</v>
+      </c>
+      <c r="P23" s="2">
         <v>100000</v>
       </c>
-      <c r="N20" s="2">
+      <c r="Q23" s="2">
         <v>30000</v>
       </c>
-      <c r="O20" s="2">
+      <c r="S23" s="1"/>
+    </row>
+    <row r="24" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="4">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
+        <v>100000</v>
+      </c>
+      <c r="K24" s="2">
         <v>30000</v>
       </c>
-      <c r="P20" s="2">
+      <c r="L24" s="2">
         <v>100000</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="M24" s="2">
+        <v>30000</v>
+      </c>
+      <c r="N24" s="2">
         <v>100000</v>
       </c>
-      <c r="R20" s="1"/>
+      <c r="O24" s="2">
+        <v>30000</v>
+      </c>
+      <c r="P24" s="2">
+        <v>100000</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>30000</v>
+      </c>
+      <c r="S24" s="1"/>
     </row>
-    <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="4">
-        <v>0</v>
-      </c>
-      <c r="C21" s="4">
-        <v>0</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0</v>
-      </c>
-      <c r="E21" s="4">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0</v>
-      </c>
-      <c r="G21" s="2">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2">
+    <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="4">
+        <v>0</v>
+      </c>
+      <c r="C25" s="4">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
         <v>30000</v>
       </c>
-      <c r="K21" s="2">
+      <c r="K25" s="2">
         <v>30000</v>
       </c>
-      <c r="L21" s="2">
-        <v>100000</v>
-      </c>
-      <c r="M21" s="2">
-        <v>100000</v>
-      </c>
-      <c r="N21" s="2">
+      <c r="L25" s="2">
         <v>30000</v>
       </c>
-      <c r="O21" s="2">
+      <c r="M25" s="2">
         <v>30000</v>
       </c>
-      <c r="P21" s="2">
-        <v>100000</v>
-      </c>
-      <c r="Q21" s="2">
-        <v>100000</v>
-      </c>
-      <c r="R21" s="1"/>
+      <c r="N25" s="2">
+        <v>30000</v>
+      </c>
+      <c r="O25" s="2">
+        <v>30000</v>
+      </c>
+      <c r="P25" s="2">
+        <v>30000</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>30000</v>
+      </c>
+      <c r="S25" s="1"/>
     </row>
-    <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" s="4">
-        <v>0</v>
-      </c>
-      <c r="C22" s="4">
-        <v>0</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" s="4">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2">
-        <v>30000</v>
-      </c>
-      <c r="K22" s="2">
-        <v>30000</v>
-      </c>
-      <c r="L22" s="2">
-        <v>30000</v>
-      </c>
-      <c r="M22" s="2">
-        <v>30000</v>
-      </c>
-      <c r="N22" s="2">
-        <v>30000</v>
-      </c>
-      <c r="O22" s="2">
-        <v>30000</v>
-      </c>
-      <c r="P22" s="2">
-        <v>30000</v>
-      </c>
-      <c r="Q22" s="2">
-        <v>30000</v>
-      </c>
-      <c r="R22" s="1"/>
-    </row>
-    <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-    </row>
-    <row r="24" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-    </row>
-    <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-    </row>
-    <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2341,9 +2646,9 @@
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
     </row>
-    <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2361,9 +2666,9 @@
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
     </row>
-    <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2381,9 +2686,9 @@
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
     </row>
-    <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2401,11 +2706,68 @@
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
     </row>
-    <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="S30" s="1"/>
+    </row>
+    <row r="31" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="S31" s="1"/>
+    </row>
+    <row r="32" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="S32" s="1"/>
+    </row>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3375,6 +3737,9 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3386,10 +3751,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA1001"/>
+  <dimension ref="A1:AA1004"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="27" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3476,7 +3841,7 @@
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3">
         <v>150000</v>
@@ -3557,7 +3922,7 @@
     </row>
     <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B3" s="3">
         <v>150000</v>
@@ -3638,7 +4003,7 @@
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B4" s="3">
         <v>150000</v>
@@ -4091,100 +4456,250 @@
     </row>
     <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="B17" s="3">
+        <v>150000</v>
+      </c>
+      <c r="C17" s="3">
+        <v>155000</v>
+      </c>
+      <c r="D17" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F17" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G17" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H17" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>282500</v>
+      </c>
+      <c r="K17" s="3">
+        <v>305000</v>
+      </c>
+      <c r="L17" s="3">
+        <v>310000</v>
+      </c>
+      <c r="M17" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N17" s="3">
+        <v>370000</v>
+      </c>
+      <c r="O17" s="3">
+        <v>395000</v>
+      </c>
+      <c r="P17" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>410000</v>
+      </c>
+      <c r="R17" s="3">
+        <v>420000</v>
+      </c>
+      <c r="S17" s="3">
+        <v>420000</v>
+      </c>
+      <c r="T17" s="3">
+        <v>420000</v>
+      </c>
+      <c r="U17" s="3">
+        <v>453000</v>
+      </c>
+      <c r="V17" s="3">
+        <v>480000</v>
+      </c>
+      <c r="W17" s="3">
+        <v>490000</v>
+      </c>
+      <c r="X17" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>500000</v>
+      </c>
       <c r="AA17" s="3"/>
     </row>
     <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="B18" s="3">
+        <v>150000</v>
+      </c>
+      <c r="C18" s="3">
+        <v>155000</v>
+      </c>
+      <c r="D18" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G18" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H18" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>282500</v>
+      </c>
+      <c r="K18" s="3">
+        <v>305000</v>
+      </c>
+      <c r="L18" s="3">
+        <v>310000</v>
+      </c>
+      <c r="M18" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N18" s="3">
+        <v>370000</v>
+      </c>
+      <c r="O18" s="3">
+        <v>395000</v>
+      </c>
+      <c r="P18" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>410000</v>
+      </c>
+      <c r="R18" s="3">
+        <v>420000</v>
+      </c>
+      <c r="S18" s="3">
+        <v>420000</v>
+      </c>
+      <c r="T18" s="3">
+        <v>420000</v>
+      </c>
+      <c r="U18" s="3">
+        <v>453000</v>
+      </c>
+      <c r="V18" s="3">
+        <v>480000</v>
+      </c>
+      <c r="W18" s="3">
+        <v>490000</v>
+      </c>
+      <c r="X18" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>500000</v>
+      </c>
       <c r="AA18" s="3"/>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="3">
+        <v>150000</v>
+      </c>
+      <c r="C19" s="3">
+        <v>155000</v>
+      </c>
+      <c r="D19" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E19" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F19" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G19" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H19" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I19" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J19" s="3">
+        <v>282500</v>
+      </c>
+      <c r="K19" s="3">
+        <v>305000</v>
+      </c>
+      <c r="L19" s="3">
+        <v>310000</v>
+      </c>
+      <c r="M19" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N19" s="3">
+        <v>370000</v>
+      </c>
+      <c r="O19" s="3">
+        <v>395000</v>
+      </c>
+      <c r="P19" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>410000</v>
+      </c>
+      <c r="R19" s="3">
+        <v>420000</v>
+      </c>
+      <c r="S19" s="3">
+        <v>420000</v>
+      </c>
+      <c r="T19" s="3">
+        <v>420000</v>
+      </c>
+      <c r="U19" s="3">
+        <v>453000</v>
+      </c>
+      <c r="V19" s="3">
+        <v>480000</v>
+      </c>
+      <c r="W19" s="3">
+        <v>490000</v>
+      </c>
+      <c r="X19" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>500000</v>
+      </c>
       <c r="AA19" s="3"/>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>9</v>
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -4213,9 +4728,9 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
-        <v>10</v>
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -4244,9 +4759,9 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>11</v>
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -4275,9 +4790,99 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+    </row>
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+    </row>
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
+    </row>
     <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5254,6 +5859,9 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5266,10 +5874,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA1001"/>
+  <dimension ref="A1:AA1004"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="27" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5358,7 +5966,7 @@
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3">
         <v>115000</v>
@@ -5441,7 +6049,7 @@
     </row>
     <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B3" s="3">
         <v>115000</v>
@@ -5524,7 +6132,7 @@
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B4" s="3">
         <v>115000</v>
@@ -6603,7 +7211,7 @@
     </row>
     <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3">
         <v>115000</v>
@@ -6612,7 +7220,7 @@
         <v>133000</v>
       </c>
       <c r="D17" s="3">
-        <v>151000</v>
+        <v>160000</v>
       </c>
       <c r="E17" s="3">
         <v>183000</v>
@@ -6624,7 +7232,7 @@
         <v>228000</v>
       </c>
       <c r="H17" s="3">
-        <v>233000</v>
+        <v>228000</v>
       </c>
       <c r="I17" s="3">
         <v>237000</v>
@@ -6636,7 +7244,7 @@
         <v>260000</v>
       </c>
       <c r="L17" s="3">
-        <v>269000</v>
+        <v>264000</v>
       </c>
       <c r="M17" s="3">
         <v>273000</v>
@@ -6686,7 +7294,7 @@
     </row>
     <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B18" s="3">
         <v>115000</v>
@@ -6695,7 +7303,7 @@
         <v>133000</v>
       </c>
       <c r="D18" s="3">
-        <v>151000</v>
+        <v>160000</v>
       </c>
       <c r="E18" s="3">
         <v>183000</v>
@@ -6719,7 +7327,7 @@
         <v>260000</v>
       </c>
       <c r="L18" s="3">
-        <v>269000</v>
+        <v>264000</v>
       </c>
       <c r="M18" s="3">
         <v>273000</v>
@@ -6767,341 +7375,587 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>28</v>
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="B19" s="3">
+        <v>115000</v>
+      </c>
+      <c r="C19" s="3">
+        <v>133000</v>
+      </c>
+      <c r="D19" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E19" s="3">
+        <v>183000</v>
+      </c>
+      <c r="F19" s="3">
+        <v>210000</v>
+      </c>
+      <c r="G19" s="3">
+        <v>228000</v>
+      </c>
+      <c r="H19" s="3">
+        <v>228000</v>
+      </c>
+      <c r="I19" s="3">
+        <v>237000</v>
+      </c>
+      <c r="J19" s="3">
+        <v>255000</v>
+      </c>
+      <c r="K19" s="3">
+        <v>260000</v>
+      </c>
+      <c r="L19" s="3">
+        <v>264000</v>
+      </c>
+      <c r="M19" s="3">
+        <v>273000</v>
+      </c>
+      <c r="N19" s="3">
+        <v>300000</v>
+      </c>
+      <c r="O19" s="3">
+        <v>319000</v>
+      </c>
+      <c r="P19" s="3">
+        <v>332000</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>346000</v>
+      </c>
+      <c r="R19" s="3">
+        <v>355000</v>
+      </c>
+      <c r="S19" s="3">
+        <v>364000</v>
+      </c>
+      <c r="T19" s="3">
+        <v>377000</v>
+      </c>
+      <c r="U19" s="3">
+        <v>413000</v>
+      </c>
+      <c r="V19" s="3">
+        <v>450000</v>
+      </c>
+      <c r="W19" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X19" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>500000</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="3">
+        <v>115000</v>
+      </c>
+      <c r="C20" s="3">
+        <v>133000</v>
+      </c>
+      <c r="D20" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>183000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>210000</v>
+      </c>
+      <c r="G20" s="3">
+        <v>228000</v>
+      </c>
+      <c r="H20" s="3">
+        <v>233000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>237000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>255000</v>
+      </c>
+      <c r="K20" s="3">
+        <v>260000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>269000</v>
+      </c>
+      <c r="M20" s="3">
+        <v>273000</v>
+      </c>
+      <c r="N20" s="3">
+        <v>300000</v>
+      </c>
+      <c r="O20" s="3">
+        <v>319000</v>
+      </c>
+      <c r="P20" s="3">
+        <v>332000</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>346000</v>
+      </c>
+      <c r="R20" s="3">
+        <v>355000</v>
+      </c>
+      <c r="S20" s="3">
+        <v>364000</v>
+      </c>
+      <c r="T20" s="3">
+        <v>377000</v>
+      </c>
+      <c r="U20" s="3">
+        <v>413000</v>
+      </c>
+      <c r="V20" s="3">
+        <v>450000</v>
+      </c>
+      <c r="W20" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X20" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>500000</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="3">
+        <v>115000</v>
+      </c>
+      <c r="C21" s="3">
+        <v>133000</v>
+      </c>
+      <c r="D21" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>183000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>210000</v>
+      </c>
+      <c r="G21" s="3">
+        <v>228000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>228000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>237000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>255000</v>
+      </c>
+      <c r="K21" s="3">
+        <v>260000</v>
+      </c>
+      <c r="L21" s="3">
+        <v>269000</v>
+      </c>
+      <c r="M21" s="3">
+        <v>273000</v>
+      </c>
+      <c r="N21" s="3">
+        <v>300000</v>
+      </c>
+      <c r="O21" s="3">
+        <v>319000</v>
+      </c>
+      <c r="P21" s="3">
+        <v>332000</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>346000</v>
+      </c>
+      <c r="R21" s="3">
+        <v>355000</v>
+      </c>
+      <c r="S21" s="3">
+        <v>364000</v>
+      </c>
+      <c r="T21" s="3">
+        <v>377000</v>
+      </c>
+      <c r="U21" s="3">
+        <v>413000</v>
+      </c>
+      <c r="V21" s="3">
+        <v>450000</v>
+      </c>
+      <c r="W21" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X21" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>500000</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3">
         <v>55000</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C22" s="3">
         <v>82000</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D22" s="3">
         <v>109000</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E22" s="3">
         <v>156000</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F22" s="3">
         <v>196000</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G22" s="3">
         <v>223000</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H22" s="3">
         <v>230000</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I22" s="3">
         <v>236000</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J22" s="3">
         <v>263000</v>
       </c>
-      <c r="K19" s="3">
+      <c r="K22" s="3">
         <v>270000</v>
       </c>
-      <c r="L19" s="3">
+      <c r="L22" s="3">
         <v>283000</v>
       </c>
-      <c r="M19" s="3">
+      <c r="M22" s="3">
         <v>290000</v>
       </c>
-      <c r="N19" s="3">
+      <c r="N22" s="3">
         <v>330000</v>
       </c>
-      <c r="O19" s="3">
+      <c r="O22" s="3">
         <v>357000</v>
       </c>
-      <c r="P19" s="3">
+      <c r="P22" s="3">
         <v>377000</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="Q22" s="3">
         <v>398000</v>
       </c>
-      <c r="R19" s="3">
+      <c r="R22" s="3">
         <v>411000</v>
       </c>
-      <c r="S19" s="3">
+      <c r="S22" s="3">
         <v>425000</v>
       </c>
-      <c r="T19" s="3">
+      <c r="T22" s="3">
         <v>445000</v>
       </c>
-      <c r="U19" s="3">
+      <c r="U22" s="3">
         <v>498000</v>
       </c>
-      <c r="V19" s="3">
+      <c r="V22" s="3">
         <v>530000</v>
       </c>
-      <c r="W19" s="3">
+      <c r="W22" s="3">
         <v>600000</v>
       </c>
-      <c r="X19" s="3">
+      <c r="X22" s="3">
         <v>600000</v>
       </c>
-      <c r="Y19" s="3">
+      <c r="Y22" s="3">
         <v>600000</v>
       </c>
-      <c r="Z19" s="3">
+      <c r="Z22" s="3">
         <v>600000</v>
       </c>
-      <c r="AA19" s="3">
+      <c r="AA22" s="3">
         <v>600000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B23" s="3">
         <v>36000</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C23" s="3">
         <v>42000</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D23" s="3">
         <v>49000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E23" s="3">
         <v>60000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F23" s="3">
         <v>69000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G23" s="3">
         <v>75000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H23" s="3">
         <v>77000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I23" s="3">
         <v>78000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J23" s="3">
         <v>85000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K23" s="3">
         <v>86000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L23" s="3">
         <v>89000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M23" s="3">
         <v>91000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N23" s="3">
         <v>100000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O23" s="3">
         <v>107000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P23" s="3">
         <v>111000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q23" s="3">
         <v>116000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R23" s="3">
         <v>119000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S23" s="3">
         <v>122000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="T23" s="3">
         <v>127000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="U23" s="3">
         <v>139000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="V23" s="3">
         <v>147000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="W23" s="3">
         <v>150000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="X23" s="3">
         <v>183000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Y23" s="3">
         <v>201000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="Z23" s="3">
         <v>221000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AA23" s="3">
         <v>250000</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B24" s="3">
         <v>36000</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C24" s="3">
         <v>42000</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D24" s="3">
         <v>49000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E24" s="3">
         <v>60000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F24" s="3">
         <v>69000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G24" s="3">
         <v>75000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H24" s="3">
         <v>77000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I24" s="3">
         <v>78000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J24" s="3">
         <v>85000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K24" s="3">
         <v>86000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L24" s="3">
         <v>89000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M24" s="3">
         <v>91000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N24" s="3">
         <v>100000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O24" s="3">
         <v>107000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P24" s="3">
         <v>111000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q24" s="3">
         <v>116000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R24" s="3">
         <v>119000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S24" s="3">
         <v>122000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T24" s="3">
         <v>127000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U24" s="3">
         <v>139000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V24" s="3">
         <v>147000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W24" s="3">
         <v>150000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X24" s="3">
         <v>183000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y24" s="3">
         <v>201000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z24" s="3">
         <v>221000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA24" s="3">
         <v>250000</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B25" s="3">
         <v>36000</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C25" s="3">
         <v>42000</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D25" s="3">
         <v>49000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E25" s="3">
         <v>60000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F25" s="3">
         <v>69000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G25" s="3">
         <v>75000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H25" s="3">
         <v>77000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I25" s="3">
         <v>78000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J25" s="3">
         <v>85000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K25" s="3">
         <v>86000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L25" s="3">
         <v>89000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M25" s="3">
         <v>91000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N25" s="3">
         <v>100000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O25" s="3">
         <v>107000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="P25" s="3">
         <v>111000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q25" s="3">
         <v>116000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="R25" s="3">
         <v>119000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S25" s="3">
         <v>122000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="T25" s="3">
         <v>127000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="U25" s="3">
         <v>139000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="V25" s="3">
         <v>147000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="W25" s="3">
         <v>150000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="X25" s="3">
         <v>183000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Y25" s="3">
         <v>201000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="Z25" s="3">
         <v>221000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AA25" s="3">
         <v>250000</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -8078,6 +8932,9 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8090,10 +8947,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA1001"/>
+  <dimension ref="A1:AA1004"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="27" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8182,7 +9039,7 @@
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
@@ -8265,7 +9122,7 @@
     </row>
     <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B3" s="3">
         <v>0</v>
@@ -8348,7 +9205,7 @@
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -9427,7 +10284,7 @@
     </row>
     <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3">
         <v>0</v>
@@ -9510,7 +10367,7 @@
     </row>
     <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B18" s="3">
         <v>0</v>
@@ -9540,7 +10397,7 @@
         <v>268000</v>
       </c>
       <c r="K18" s="3">
-        <v>288000</v>
+        <v>280000</v>
       </c>
       <c r="L18" s="3">
         <v>291000</v>
@@ -9591,9 +10448,9 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>28</v>
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="B19" s="3">
         <v>0</v>
@@ -9674,258 +10531,504 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>198000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>222000</v>
+      </c>
+      <c r="G20" s="3">
+        <v>233000</v>
+      </c>
+      <c r="H20" s="3">
+        <v>257000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>262000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>268000</v>
+      </c>
+      <c r="K20" s="3">
+        <v>280000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>291000</v>
+      </c>
+      <c r="M20" s="3">
+        <v>326000</v>
+      </c>
+      <c r="N20" s="3">
+        <v>350000</v>
+      </c>
+      <c r="O20" s="3">
+        <v>361000</v>
+      </c>
+      <c r="P20" s="3">
+        <v>373000</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>390000</v>
+      </c>
+      <c r="R20" s="3">
+        <v>402000</v>
+      </c>
+      <c r="S20" s="3">
+        <v>407000</v>
+      </c>
+      <c r="T20" s="3">
+        <v>414000</v>
+      </c>
+      <c r="U20" s="3">
+        <v>442000</v>
+      </c>
+      <c r="V20" s="3">
+        <v>460000</v>
+      </c>
+      <c r="W20" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X20" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>500000</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>198000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>222000</v>
+      </c>
+      <c r="G21" s="3">
+        <v>233000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>257000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>262000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>268000</v>
+      </c>
+      <c r="K21" s="3">
+        <v>288000</v>
+      </c>
+      <c r="L21" s="3">
+        <v>291000</v>
+      </c>
+      <c r="M21" s="3">
+        <v>326000</v>
+      </c>
+      <c r="N21" s="3">
+        <v>350000</v>
+      </c>
+      <c r="O21" s="3">
+        <v>361000</v>
+      </c>
+      <c r="P21" s="3">
+        <v>373000</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>390000</v>
+      </c>
+      <c r="R21" s="3">
+        <v>402000</v>
+      </c>
+      <c r="S21" s="3">
+        <v>407000</v>
+      </c>
+      <c r="T21" s="3">
+        <v>414000</v>
+      </c>
+      <c r="U21" s="3">
+        <v>442000</v>
+      </c>
+      <c r="V21" s="3">
+        <v>460000</v>
+      </c>
+      <c r="W21" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X21" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>500000</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>198000</v>
+      </c>
+      <c r="F22" s="3">
+        <v>222000</v>
+      </c>
+      <c r="G22" s="3">
+        <v>233000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>257000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>262000</v>
+      </c>
+      <c r="J22" s="3">
+        <v>268000</v>
+      </c>
+      <c r="K22" s="3">
+        <v>280000</v>
+      </c>
+      <c r="L22" s="3">
+        <v>291000</v>
+      </c>
+      <c r="M22" s="3">
+        <v>326000</v>
+      </c>
+      <c r="N22" s="3">
+        <v>350000</v>
+      </c>
+      <c r="O22" s="3">
+        <v>361000</v>
+      </c>
+      <c r="P22" s="3">
+        <v>373000</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>390000</v>
+      </c>
+      <c r="R22" s="3">
+        <v>402000</v>
+      </c>
+      <c r="S22" s="3">
+        <v>407000</v>
+      </c>
+      <c r="T22" s="3">
+        <v>414000</v>
+      </c>
+      <c r="U22" s="3">
+        <v>442000</v>
+      </c>
+      <c r="V22" s="3">
+        <v>460000</v>
+      </c>
+      <c r="W22" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X22" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>500000</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="3">
-        <v>0</v>
-      </c>
-      <c r="C20" s="3">
-        <v>0</v>
-      </c>
-      <c r="D20" s="3">
+      <c r="B23" s="3">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3">
         <v>158000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E23" s="3">
         <v>180000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F23" s="3">
         <v>202000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G23" s="3">
         <v>213000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H23" s="3">
         <v>235000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I23" s="3">
         <v>240000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J23" s="3">
         <v>245000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K23" s="3">
         <v>257000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L23" s="3">
         <v>267000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M23" s="3">
         <v>300000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N23" s="3">
         <v>311000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O23" s="3">
         <v>321000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P23" s="3">
         <v>332000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q23" s="3">
         <v>348000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R23" s="3">
         <v>358000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S23" s="3">
         <v>363000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="T23" s="3">
         <v>369000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="U23" s="3">
         <v>395000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="V23" s="3">
         <v>395000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="W23" s="3">
         <v>400000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="X23" s="3">
         <v>400000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Y23" s="3">
         <v>400000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="Z23" s="3">
         <v>400000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AA23" s="3">
         <v>400000</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="3">
-        <v>0</v>
-      </c>
-      <c r="C21" s="3">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3">
+      <c r="B24" s="3">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3">
         <v>52000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E24" s="3">
         <v>59000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F24" s="3">
         <v>66000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G24" s="3">
         <v>69000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H24" s="3">
         <v>76000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I24" s="3">
         <v>78000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J24" s="3">
         <v>80000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K24" s="3">
         <v>84000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L24" s="3">
         <v>87000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M24" s="3">
         <v>98000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N24" s="3">
         <v>105000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O24" s="3">
         <v>108000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P24" s="3">
         <v>112000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q24" s="3">
         <v>117000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R24" s="3">
         <v>121000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S24" s="3">
         <v>122000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T24" s="3">
         <v>124000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U24" s="3">
         <v>133000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V24" s="3">
         <v>138000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W24" s="3">
         <v>151000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X24" s="3">
         <v>168000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y24" s="3">
         <v>186000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z24" s="3">
         <v>204000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA24" s="3">
         <v>230000</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B25" s="3">
         <v>124000</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C25" s="3">
         <v>139000</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D25" s="3">
         <v>141000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E25" s="3">
         <v>151000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F25" s="3">
         <v>161000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G25" s="3">
         <v>277000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H25" s="3">
         <v>298000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I25" s="3">
         <v>303000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J25" s="3">
         <v>308000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K25" s="3">
         <v>319000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L25" s="3">
         <v>319000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M25" s="3">
         <v>319000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N25" s="3">
         <v>319000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O25" s="3">
         <v>319000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="P25" s="3">
         <v>319000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q25" s="3">
         <v>319000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="R25" s="3">
         <v>319000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S25" s="3">
         <v>319000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="T25" s="3">
         <v>319000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="U25" s="3">
         <v>319000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="V25" s="3">
         <v>319000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="W25" s="3">
         <v>319000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="X25" s="3">
         <v>319000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Y25" s="3">
         <v>319000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="Z25" s="3">
         <v>319000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AA25" s="3">
         <v>319000</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -10902,6 +12005,9 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/policy_20260801.xlsx
+++ b/policy_20260801.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ETW\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AED7530-D5B7-4565-B063-557BA978A5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33BD7975-1D86-47B4-8AC7-D4AFD92EAF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5160" yWindow="3360" windowWidth="26505" windowHeight="14550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6195" yWindow="4395" windowWidth="26505" windowHeight="14550" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="추가지원금" sheetId="1" r:id="rId1"/>
@@ -4086,310 +4086,810 @@
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
+      <c r="B5" s="3">
+        <v>150000</v>
+      </c>
+      <c r="C5" s="3">
+        <v>155000</v>
+      </c>
+      <c r="D5" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E5" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F5" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G5" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H5" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I5" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J5" s="3">
+        <v>282500</v>
+      </c>
+      <c r="K5" s="3">
+        <v>305000</v>
+      </c>
+      <c r="L5" s="3">
+        <v>310000</v>
+      </c>
+      <c r="M5" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N5" s="3">
+        <v>370000</v>
+      </c>
+      <c r="O5" s="3">
+        <v>395000</v>
+      </c>
+      <c r="P5" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>410000</v>
+      </c>
+      <c r="R5" s="3">
+        <v>420000</v>
+      </c>
+      <c r="S5" s="3">
+        <v>420000</v>
+      </c>
+      <c r="T5" s="3">
+        <v>420000</v>
+      </c>
+      <c r="U5" s="3">
+        <v>453000</v>
+      </c>
+      <c r="V5" s="3">
+        <v>480000</v>
+      </c>
+      <c r="W5" s="3">
+        <v>490000</v>
+      </c>
+      <c r="X5" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>500000</v>
+      </c>
       <c r="AA5" s="3"/>
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
+      <c r="B6" s="3">
+        <v>150000</v>
+      </c>
+      <c r="C6" s="3">
+        <v>155000</v>
+      </c>
+      <c r="D6" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E6" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F6" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G6" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H6" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I6" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J6" s="3">
+        <v>282500</v>
+      </c>
+      <c r="K6" s="3">
+        <v>305000</v>
+      </c>
+      <c r="L6" s="3">
+        <v>310000</v>
+      </c>
+      <c r="M6" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N6" s="3">
+        <v>370000</v>
+      </c>
+      <c r="O6" s="3">
+        <v>395000</v>
+      </c>
+      <c r="P6" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>410000</v>
+      </c>
+      <c r="R6" s="3">
+        <v>420000</v>
+      </c>
+      <c r="S6" s="3">
+        <v>420000</v>
+      </c>
+      <c r="T6" s="3">
+        <v>420000</v>
+      </c>
+      <c r="U6" s="3">
+        <v>453000</v>
+      </c>
+      <c r="V6" s="3">
+        <v>480000</v>
+      </c>
+      <c r="W6" s="3">
+        <v>490000</v>
+      </c>
+      <c r="X6" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>500000</v>
+      </c>
       <c r="AA6" s="3"/>
     </row>
     <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
+      <c r="B7" s="3">
+        <v>150000</v>
+      </c>
+      <c r="C7" s="3">
+        <v>155000</v>
+      </c>
+      <c r="D7" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E7" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F7" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G7" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H7" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I7" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J7" s="3">
+        <v>282500</v>
+      </c>
+      <c r="K7" s="3">
+        <v>305000</v>
+      </c>
+      <c r="L7" s="3">
+        <v>310000</v>
+      </c>
+      <c r="M7" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N7" s="3">
+        <v>370000</v>
+      </c>
+      <c r="O7" s="3">
+        <v>395000</v>
+      </c>
+      <c r="P7" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>410000</v>
+      </c>
+      <c r="R7" s="3">
+        <v>420000</v>
+      </c>
+      <c r="S7" s="3">
+        <v>420000</v>
+      </c>
+      <c r="T7" s="3">
+        <v>420000</v>
+      </c>
+      <c r="U7" s="3">
+        <v>453000</v>
+      </c>
+      <c r="V7" s="3">
+        <v>480000</v>
+      </c>
+      <c r="W7" s="3">
+        <v>490000</v>
+      </c>
+      <c r="X7" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>500000</v>
+      </c>
       <c r="AA7" s="3"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
+      <c r="B8" s="3">
+        <v>150000</v>
+      </c>
+      <c r="C8" s="3">
+        <v>155000</v>
+      </c>
+      <c r="D8" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F8" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G8" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H8" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I8" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J8" s="3">
+        <v>282500</v>
+      </c>
+      <c r="K8" s="3">
+        <v>305000</v>
+      </c>
+      <c r="L8" s="3">
+        <v>310000</v>
+      </c>
+      <c r="M8" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N8" s="3">
+        <v>370000</v>
+      </c>
+      <c r="O8" s="3">
+        <v>395000</v>
+      </c>
+      <c r="P8" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>410000</v>
+      </c>
+      <c r="R8" s="3">
+        <v>420000</v>
+      </c>
+      <c r="S8" s="3">
+        <v>420000</v>
+      </c>
+      <c r="T8" s="3">
+        <v>420000</v>
+      </c>
+      <c r="U8" s="3">
+        <v>453000</v>
+      </c>
+      <c r="V8" s="3">
+        <v>480000</v>
+      </c>
+      <c r="W8" s="3">
+        <v>490000</v>
+      </c>
+      <c r="X8" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>500000</v>
+      </c>
       <c r="AA8" s="3"/>
     </row>
     <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
+      <c r="B9" s="3">
+        <v>150000</v>
+      </c>
+      <c r="C9" s="3">
+        <v>155000</v>
+      </c>
+      <c r="D9" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G9" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H9" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>282500</v>
+      </c>
+      <c r="K9" s="3">
+        <v>305000</v>
+      </c>
+      <c r="L9" s="3">
+        <v>310000</v>
+      </c>
+      <c r="M9" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N9" s="3">
+        <v>370000</v>
+      </c>
+      <c r="O9" s="3">
+        <v>395000</v>
+      </c>
+      <c r="P9" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>410000</v>
+      </c>
+      <c r="R9" s="3">
+        <v>420000</v>
+      </c>
+      <c r="S9" s="3">
+        <v>420000</v>
+      </c>
+      <c r="T9" s="3">
+        <v>420000</v>
+      </c>
+      <c r="U9" s="3">
+        <v>453000</v>
+      </c>
+      <c r="V9" s="3">
+        <v>480000</v>
+      </c>
+      <c r="W9" s="3">
+        <v>490000</v>
+      </c>
+      <c r="X9" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>500000</v>
+      </c>
       <c r="AA9" s="3"/>
     </row>
     <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
+      <c r="B10" s="3">
+        <v>150000</v>
+      </c>
+      <c r="C10" s="3">
+        <v>155000</v>
+      </c>
+      <c r="D10" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>282500</v>
+      </c>
+      <c r="K10" s="3">
+        <v>305000</v>
+      </c>
+      <c r="L10" s="3">
+        <v>310000</v>
+      </c>
+      <c r="M10" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N10" s="3">
+        <v>370000</v>
+      </c>
+      <c r="O10" s="3">
+        <v>395000</v>
+      </c>
+      <c r="P10" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>410000</v>
+      </c>
+      <c r="R10" s="3">
+        <v>420000</v>
+      </c>
+      <c r="S10" s="3">
+        <v>420000</v>
+      </c>
+      <c r="T10" s="3">
+        <v>420000</v>
+      </c>
+      <c r="U10" s="3">
+        <v>453000</v>
+      </c>
+      <c r="V10" s="3">
+        <v>480000</v>
+      </c>
+      <c r="W10" s="3">
+        <v>490000</v>
+      </c>
+      <c r="X10" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>500000</v>
+      </c>
       <c r="AA10" s="3"/>
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
+      <c r="B11" s="3">
+        <v>150000</v>
+      </c>
+      <c r="C11" s="3">
+        <v>155000</v>
+      </c>
+      <c r="D11" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E11" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F11" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G11" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H11" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I11" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J11" s="3">
+        <v>282500</v>
+      </c>
+      <c r="K11" s="3">
+        <v>305000</v>
+      </c>
+      <c r="L11" s="3">
+        <v>310000</v>
+      </c>
+      <c r="M11" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N11" s="3">
+        <v>370000</v>
+      </c>
+      <c r="O11" s="3">
+        <v>395000</v>
+      </c>
+      <c r="P11" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>410000</v>
+      </c>
+      <c r="R11" s="3">
+        <v>420000</v>
+      </c>
+      <c r="S11" s="3">
+        <v>420000</v>
+      </c>
+      <c r="T11" s="3">
+        <v>420000</v>
+      </c>
+      <c r="U11" s="3">
+        <v>453000</v>
+      </c>
+      <c r="V11" s="3">
+        <v>480000</v>
+      </c>
+      <c r="W11" s="3">
+        <v>490000</v>
+      </c>
+      <c r="X11" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>500000</v>
+      </c>
       <c r="AA11" s="3"/>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
+      <c r="B12" s="3">
+        <v>150000</v>
+      </c>
+      <c r="C12" s="3">
+        <v>155000</v>
+      </c>
+      <c r="D12" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F12" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G12" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H12" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I12" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J12" s="3">
+        <v>282500</v>
+      </c>
+      <c r="K12" s="3">
+        <v>305000</v>
+      </c>
+      <c r="L12" s="3">
+        <v>310000</v>
+      </c>
+      <c r="M12" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N12" s="3">
+        <v>370000</v>
+      </c>
+      <c r="O12" s="3">
+        <v>395000</v>
+      </c>
+      <c r="P12" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>410000</v>
+      </c>
+      <c r="R12" s="3">
+        <v>420000</v>
+      </c>
+      <c r="S12" s="3">
+        <v>420000</v>
+      </c>
+      <c r="T12" s="3">
+        <v>420000</v>
+      </c>
+      <c r="U12" s="3">
+        <v>453000</v>
+      </c>
+      <c r="V12" s="3">
+        <v>480000</v>
+      </c>
+      <c r="W12" s="3">
+        <v>490000</v>
+      </c>
+      <c r="X12" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>500000</v>
+      </c>
       <c r="AA12" s="3"/>
     </row>
     <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
+      <c r="B13" s="3">
+        <v>150000</v>
+      </c>
+      <c r="C13" s="3">
+        <v>155000</v>
+      </c>
+      <c r="D13" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E13" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F13" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G13" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H13" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I13" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J13" s="3">
+        <v>282500</v>
+      </c>
+      <c r="K13" s="3">
+        <v>305000</v>
+      </c>
+      <c r="L13" s="3">
+        <v>310000</v>
+      </c>
+      <c r="M13" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N13" s="3">
+        <v>370000</v>
+      </c>
+      <c r="O13" s="3">
+        <v>395000</v>
+      </c>
+      <c r="P13" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>410000</v>
+      </c>
+      <c r="R13" s="3">
+        <v>420000</v>
+      </c>
+      <c r="S13" s="3">
+        <v>420000</v>
+      </c>
+      <c r="T13" s="3">
+        <v>420000</v>
+      </c>
+      <c r="U13" s="3">
+        <v>453000</v>
+      </c>
+      <c r="V13" s="3">
+        <v>480000</v>
+      </c>
+      <c r="W13" s="3">
+        <v>490000</v>
+      </c>
+      <c r="X13" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>500000</v>
+      </c>
       <c r="AA13" s="3"/>
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
+      <c r="B14" s="3">
+        <v>350000</v>
+      </c>
+      <c r="C14" s="3">
+        <v>355000</v>
+      </c>
+      <c r="D14" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>415000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>420000</v>
+      </c>
+      <c r="G14" s="3">
+        <v>445000</v>
+      </c>
+      <c r="H14" s="3">
+        <v>465000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>470000</v>
+      </c>
+      <c r="J14" s="3">
+        <v>482500</v>
+      </c>
+      <c r="K14" s="3">
+        <v>505000</v>
+      </c>
+      <c r="L14" s="3">
+        <v>510000</v>
+      </c>
+      <c r="M14" s="3">
+        <v>533000</v>
+      </c>
+      <c r="N14" s="3">
+        <v>570000</v>
+      </c>
+      <c r="O14" s="3">
+        <v>595000</v>
+      </c>
+      <c r="P14" s="3">
+        <v>605000</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>610000</v>
+      </c>
+      <c r="R14" s="3">
+        <v>620000</v>
+      </c>
+      <c r="S14" s="3">
+        <v>620000</v>
+      </c>
+      <c r="T14" s="3">
+        <v>620000</v>
+      </c>
+      <c r="U14" s="3">
+        <v>653000</v>
+      </c>
+      <c r="V14" s="3">
+        <v>680000</v>
+      </c>
+      <c r="W14" s="3">
+        <v>680000</v>
+      </c>
+      <c r="X14" s="3">
+        <v>680000</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>680000</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>680000</v>
+      </c>
       <c r="AA14" s="3"/>
     </row>
     <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4427,31 +4927,81 @@
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
+      <c r="B16" s="3">
+        <v>150000</v>
+      </c>
+      <c r="C16" s="3">
+        <v>155000</v>
+      </c>
+      <c r="D16" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E16" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F16" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G16" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H16" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I16" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J16" s="3">
+        <v>282500</v>
+      </c>
+      <c r="K16" s="3">
+        <v>305000</v>
+      </c>
+      <c r="L16" s="3">
+        <v>310000</v>
+      </c>
+      <c r="M16" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N16" s="3">
+        <v>370000</v>
+      </c>
+      <c r="O16" s="3">
+        <v>395000</v>
+      </c>
+      <c r="P16" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>410000</v>
+      </c>
+      <c r="R16" s="3">
+        <v>420000</v>
+      </c>
+      <c r="S16" s="3">
+        <v>420000</v>
+      </c>
+      <c r="T16" s="3">
+        <v>420000</v>
+      </c>
+      <c r="U16" s="3">
+        <v>453000</v>
+      </c>
+      <c r="V16" s="3">
+        <v>480000</v>
+      </c>
+      <c r="W16" s="3">
+        <v>490000</v>
+      </c>
+      <c r="X16" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y16" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>500000</v>
+      </c>
       <c r="AA16" s="3"/>
     </row>
     <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4701,186 +5251,486 @@
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
+      <c r="B20" s="3">
+        <v>150000</v>
+      </c>
+      <c r="C20" s="3">
+        <v>155000</v>
+      </c>
+      <c r="D20" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G20" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H20" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>282500</v>
+      </c>
+      <c r="K20" s="3">
+        <v>305000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>310000</v>
+      </c>
+      <c r="M20" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N20" s="3">
+        <v>370000</v>
+      </c>
+      <c r="O20" s="3">
+        <v>395000</v>
+      </c>
+      <c r="P20" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>410000</v>
+      </c>
+      <c r="R20" s="3">
+        <v>420000</v>
+      </c>
+      <c r="S20" s="3">
+        <v>420000</v>
+      </c>
+      <c r="T20" s="3">
+        <v>420000</v>
+      </c>
+      <c r="U20" s="3">
+        <v>453000</v>
+      </c>
+      <c r="V20" s="3">
+        <v>480000</v>
+      </c>
+      <c r="W20" s="3">
+        <v>490000</v>
+      </c>
+      <c r="X20" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>500000</v>
+      </c>
       <c r="AA20" s="3"/>
     </row>
     <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
+      <c r="B21" s="3">
+        <v>150000</v>
+      </c>
+      <c r="C21" s="3">
+        <v>155000</v>
+      </c>
+      <c r="D21" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G21" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>282500</v>
+      </c>
+      <c r="K21" s="3">
+        <v>305000</v>
+      </c>
+      <c r="L21" s="3">
+        <v>310000</v>
+      </c>
+      <c r="M21" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N21" s="3">
+        <v>370000</v>
+      </c>
+      <c r="O21" s="3">
+        <v>395000</v>
+      </c>
+      <c r="P21" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>410000</v>
+      </c>
+      <c r="R21" s="3">
+        <v>420000</v>
+      </c>
+      <c r="S21" s="3">
+        <v>420000</v>
+      </c>
+      <c r="T21" s="3">
+        <v>420000</v>
+      </c>
+      <c r="U21" s="3">
+        <v>453000</v>
+      </c>
+      <c r="V21" s="3">
+        <v>480000</v>
+      </c>
+      <c r="W21" s="3">
+        <v>490000</v>
+      </c>
+      <c r="X21" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>500000</v>
+      </c>
       <c r="AA21" s="3"/>
     </row>
     <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
+      <c r="B22" s="3">
+        <v>150000</v>
+      </c>
+      <c r="C22" s="3">
+        <v>155000</v>
+      </c>
+      <c r="D22" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F22" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G22" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>270000</v>
+      </c>
+      <c r="J22" s="3">
+        <v>282500</v>
+      </c>
+      <c r="K22" s="3">
+        <v>305000</v>
+      </c>
+      <c r="L22" s="3">
+        <v>310000</v>
+      </c>
+      <c r="M22" s="3">
+        <v>333000</v>
+      </c>
+      <c r="N22" s="3">
+        <v>370000</v>
+      </c>
+      <c r="O22" s="3">
+        <v>395000</v>
+      </c>
+      <c r="P22" s="3">
+        <v>405000</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>410000</v>
+      </c>
+      <c r="R22" s="3">
+        <v>420000</v>
+      </c>
+      <c r="S22" s="3">
+        <v>420000</v>
+      </c>
+      <c r="T22" s="3">
+        <v>420000</v>
+      </c>
+      <c r="U22" s="3">
+        <v>453000</v>
+      </c>
+      <c r="V22" s="3">
+        <v>480000</v>
+      </c>
+      <c r="W22" s="3">
+        <v>490000</v>
+      </c>
+      <c r="X22" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>500000</v>
+      </c>
       <c r="AA22" s="3"/>
     </row>
     <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
-      <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="3"/>
+      <c r="B23" s="3">
+        <v>54000</v>
+      </c>
+      <c r="C23" s="3">
+        <v>55000</v>
+      </c>
+      <c r="D23" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>67000</v>
+      </c>
+      <c r="F23" s="3">
+        <v>68000</v>
+      </c>
+      <c r="G23" s="3">
+        <v>73000</v>
+      </c>
+      <c r="H23" s="3">
+        <v>78000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>79000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>81000</v>
+      </c>
+      <c r="K23" s="3">
+        <v>86000</v>
+      </c>
+      <c r="L23" s="3">
+        <v>87000</v>
+      </c>
+      <c r="M23" s="3">
+        <v>92000</v>
+      </c>
+      <c r="N23" s="3">
+        <v>100000</v>
+      </c>
+      <c r="O23" s="3">
+        <v>105000</v>
+      </c>
+      <c r="P23" s="3">
+        <v>107000</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>108000</v>
+      </c>
+      <c r="R23" s="3">
+        <v>110000</v>
+      </c>
+      <c r="S23" s="3">
+        <v>110000</v>
+      </c>
+      <c r="T23" s="3">
+        <v>110000</v>
+      </c>
+      <c r="U23" s="3">
+        <v>129000</v>
+      </c>
+      <c r="V23" s="3">
+        <v>150000</v>
+      </c>
+      <c r="W23" s="3">
+        <v>154000</v>
+      </c>
+      <c r="X23" s="3">
+        <v>170000</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>170000</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>170000</v>
+      </c>
       <c r="AA23" s="3"/>
     </row>
     <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="3"/>
+      <c r="B24" s="3">
+        <v>151000</v>
+      </c>
+      <c r="C24" s="3">
+        <v>157000</v>
+      </c>
+      <c r="D24" s="3">
+        <v>205000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>225000</v>
+      </c>
+      <c r="F24" s="3">
+        <v>230000</v>
+      </c>
+      <c r="G24" s="3">
+        <v>258000</v>
+      </c>
+      <c r="H24" s="3">
+        <v>281000</v>
+      </c>
+      <c r="I24" s="3">
+        <v>287000</v>
+      </c>
+      <c r="J24" s="3">
+        <v>301000</v>
+      </c>
+      <c r="K24" s="3">
+        <v>326000</v>
+      </c>
+      <c r="L24" s="3">
+        <v>332000</v>
+      </c>
+      <c r="M24" s="3">
+        <v>357000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>400000</v>
+      </c>
+      <c r="O24" s="3">
+        <v>400000</v>
+      </c>
+      <c r="P24" s="3">
+        <v>400000</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>400000</v>
+      </c>
+      <c r="R24" s="3">
+        <v>400000</v>
+      </c>
+      <c r="S24" s="3">
+        <v>400000</v>
+      </c>
+      <c r="T24" s="3">
+        <v>400000</v>
+      </c>
+      <c r="U24" s="3">
+        <v>400000</v>
+      </c>
+      <c r="V24" s="3">
+        <v>400000</v>
+      </c>
+      <c r="W24" s="3">
+        <v>400000</v>
+      </c>
+      <c r="X24" s="3">
+        <v>400000</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>400000</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>400000</v>
+      </c>
       <c r="AA24" s="3"/>
     </row>
     <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="3"/>
+      <c r="B25" s="3">
+        <v>80000</v>
+      </c>
+      <c r="C25" s="3">
+        <v>80000</v>
+      </c>
+      <c r="D25" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E25" s="3">
+        <v>87000</v>
+      </c>
+      <c r="F25" s="3">
+        <v>88000</v>
+      </c>
+      <c r="G25" s="3">
+        <v>91000</v>
+      </c>
+      <c r="H25" s="3">
+        <v>93000</v>
+      </c>
+      <c r="I25" s="3">
+        <v>94000</v>
+      </c>
+      <c r="J25" s="3">
+        <v>95000</v>
+      </c>
+      <c r="K25" s="3">
+        <v>98000</v>
+      </c>
+      <c r="L25" s="3">
+        <v>98000</v>
+      </c>
+      <c r="M25" s="3">
+        <v>101500</v>
+      </c>
+      <c r="N25" s="3">
+        <v>106000</v>
+      </c>
+      <c r="O25" s="3">
+        <v>108000</v>
+      </c>
+      <c r="P25" s="3">
+        <v>109000</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>110000</v>
+      </c>
+      <c r="R25" s="3">
+        <v>111000</v>
+      </c>
+      <c r="S25" s="3">
+        <v>111000</v>
+      </c>
+      <c r="T25" s="3">
+        <v>111000</v>
+      </c>
+      <c r="U25" s="3">
+        <v>121000</v>
+      </c>
+      <c r="V25" s="3">
+        <v>130000</v>
+      </c>
+      <c r="W25" s="3">
+        <v>130000</v>
+      </c>
+      <c r="X25" s="3">
+        <v>130000</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>130000</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>130000</v>
+      </c>
       <c r="AA25" s="3"/>
     </row>
     <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
